--- a/output/pdf_financials_xlsx/DTWO.xlsx
+++ b/output/pdf_financials_xlsx/DTWO.xlsx
@@ -900,10 +900,10 @@
         <v>0</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>0.001329</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>0.0009120000000000001</v>
       </c>
       <c r="G12" s="3" t="n">
         <v>0</v>
@@ -915,7 +915,7 @@
         <v>0</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0</v>
+        <v>0.010943</v>
       </c>
       <c r="K12" s="3" t="n">
         <v>0</v>
@@ -924,7 +924,7 @@
         <v>0</v>
       </c>
       <c r="M12" s="3" t="n">
-        <v>0</v>
+        <v>0.028172</v>
       </c>
     </row>
     <row r="13">
@@ -1613,10 +1613,10 @@
         <v>-1.351757</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-1.435586</v>
+        <v>-1.436915</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-0.8319879999999999</v>
+        <v>-0.8329</v>
       </c>
       <c r="G27" s="3" t="n">
         <v>-1.518168</v>
@@ -1628,7 +1628,7 @@
         <v>-0.324412</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>-20.361436</v>
+        <v>-20.372379</v>
       </c>
       <c r="K27" s="3" t="n">
         <v>-1.469264</v>
@@ -1637,7 +1637,7 @@
         <v>2.791124</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>-0.217119</v>
+        <v>-0.245291</v>
       </c>
     </row>
     <row r="28">
@@ -1699,10 +1699,10 @@
         <v>-1.351757</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-1.435586</v>
+        <v>-1.436915</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-0.8319879999999999</v>
+        <v>-0.8329</v>
       </c>
       <c r="G29" s="3" t="n">
         <v>-1.518168</v>
@@ -1714,7 +1714,7 @@
         <v>-0.324412</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>-20.361436</v>
+        <v>-20.372379</v>
       </c>
       <c r="K29" s="3" t="n">
         <v>-1.469264</v>
@@ -1723,7 +1723,7 @@
         <v>2.791124</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>-0.217119</v>
+        <v>-0.245291</v>
       </c>
     </row>
     <row r="30">
@@ -1917,10 +1917,10 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>5.1e-05</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.198362</v>
       </c>
       <c r="D34" s="3" t="n">
         <v>0.30085</v>
@@ -2003,10 +2003,10 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>5.1e-05</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.198362</v>
       </c>
       <c r="D36" s="3" t="n">
         <v>0.308119</v>
@@ -2519,10 +2519,10 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.014119</v>
+        <v>0.014068</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.272909</v>
+        <v>0.074547</v>
       </c>
       <c r="D48" s="3" t="n">
         <v>0.016126</v>
@@ -11556,7 +11556,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -12008,7 +12008,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E76" s="5" t="n">
@@ -32516,7 +32516,7 @@
       </c>
       <c r="D353" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E353" t="inlineStr">
@@ -37046,7 +37046,7 @@
       </c>
       <c r="D414" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E414" t="inlineStr">

--- a/output/pdf_financials_xlsx/DTWO.xlsx
+++ b/output/pdf_financials_xlsx/DTWO.xlsx
@@ -679,16 +679,16 @@
         <v>0.290096</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>0.033782</v>
+        <v>0.369337</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>0.044269</v>
+        <v>0.470962</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>0.081201</v>
+        <v>0.328887</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>0.052669</v>
+        <v>0.300166</v>
       </c>
       <c r="G7" s="3" t="n">
         <v>0.324169</v>
@@ -808,16 +808,16 @@
         <v>0.421181</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>0.038073</v>
+        <v>0.373628</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>0.04821</v>
+        <v>0.474903</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>0.083271</v>
+        <v>0.330957</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>0.054565</v>
+        <v>0.302062</v>
       </c>
       <c r="G10" s="3" t="n">
         <v>0.32552</v>
@@ -3343,10 +3343,10 @@
         <v>0.141403</v>
       </c>
       <c r="D66" s="3" t="n">
-        <v>0</v>
+        <v>0.163372</v>
       </c>
       <c r="E66" s="3" t="n">
-        <v>0</v>
+        <v>0.018293</v>
       </c>
       <c r="F66" s="3" t="n">
         <v>0</v>
@@ -4319,13 +4319,13 @@
         <v>21.69026</v>
       </c>
       <c r="D88" s="3" t="n">
-        <v>0</v>
+        <v>23.503887</v>
       </c>
       <c r="E88" s="3" t="n">
-        <v>0</v>
+        <v>26.138442</v>
       </c>
       <c r="F88" s="3" t="n">
-        <v>0</v>
+        <v>27.87689</v>
       </c>
       <c r="G88" s="3" t="n">
         <v>28.182145</v>
@@ -4491,13 +4491,13 @@
         <v>2.338509</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>2.564322</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>3.230911</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>3.030553</v>
       </c>
       <c r="G92" s="3" t="n">
         <v>3.290298</v>
@@ -9618,7 +9618,11 @@
           <t>Marketable securities – Note 5</t>
         </is>
       </c>
-      <c r="D44" t="inlineStr"/>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>ShortTermInvestments</t>
+        </is>
+      </c>
       <c r="E44" t="inlineStr">
         <is>
           <t>-</t>
@@ -9764,7 +9768,11 @@
           <t>Prepaid expenses – Note 9</t>
         </is>
       </c>
-      <c r="D46" t="inlineStr"/>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>PrepaidAssets</t>
+        </is>
+      </c>
       <c r="E46" t="inlineStr">
         <is>
           <t>-</t>
@@ -10444,7 +10452,11 @@
           <t>Loans payable – Note 10</t>
         </is>
       </c>
-      <c r="D55" t="inlineStr"/>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>CurrentDebt</t>
+        </is>
+      </c>
       <c r="E55" t="inlineStr">
         <is>
           <t>-</t>
@@ -10520,7 +10532,11 @@
           <t>Share capital – Note 8</t>
         </is>
       </c>
-      <c r="D56" t="inlineStr"/>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>CapitalStock</t>
+        </is>
+      </c>
       <c r="E56" t="inlineStr">
         <is>
           <t>-</t>
@@ -10594,7 +10610,11 @@
           <t>Contributed surplus – Note 8</t>
         </is>
       </c>
-      <c r="D57" t="inlineStr"/>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E57" t="inlineStr">
         <is>
           <t>-</t>
@@ -11256,7 +11276,11 @@
           <t>Due to related parties – Note 8</t>
         </is>
       </c>
-      <c r="D66" t="inlineStr"/>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>OtherPayable</t>
+        </is>
+      </c>
       <c r="E66" t="inlineStr">
         <is>
           <t>-</t>
@@ -11330,7 +11354,11 @@
           <t>Share capital – Note 7</t>
         </is>
       </c>
-      <c r="D67" t="inlineStr"/>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>CapitalStock</t>
+        </is>
+      </c>
       <c r="E67" t="inlineStr">
         <is>
           <t>-</t>
@@ -11402,7 +11430,11 @@
           <t>Contributed surplus – Note 7</t>
         </is>
       </c>
-      <c r="D68" t="inlineStr"/>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E68" t="inlineStr">
         <is>
           <t>-</t>
@@ -11784,7 +11816,11 @@
           <t>Due to related parties – Note 7</t>
         </is>
       </c>
-      <c r="D73" t="inlineStr"/>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>OtherPayable</t>
+        </is>
+      </c>
       <c r="E73" t="inlineStr">
         <is>
           <t>-</t>
@@ -11858,7 +11894,11 @@
           <t>Share capital – Note 6</t>
         </is>
       </c>
-      <c r="D74" t="inlineStr"/>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>CapitalStock</t>
+        </is>
+      </c>
       <c r="E74" t="inlineStr">
         <is>
           <t>-</t>
@@ -11932,7 +11972,11 @@
           <t>Contributed surplus – Note 6</t>
         </is>
       </c>
-      <c r="D75" t="inlineStr"/>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E75" t="inlineStr">
         <is>
           <t>-</t>
@@ -35750,7 +35794,11 @@
           <t>Administration fees – Note 9</t>
         </is>
       </c>
-      <c r="D396" t="inlineStr"/>
+      <c r="D396" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E396" t="inlineStr">
         <is>
           <t>-</t>
@@ -35972,7 +36020,11 @@
           <t>Consulting fees – Note 9</t>
         </is>
       </c>
-      <c r="D399" t="inlineStr"/>
+      <c r="D399" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E399" t="inlineStr">
         <is>
           <t>-</t>
@@ -36466,7 +36518,11 @@
           <t>Rent – Note 9</t>
         </is>
       </c>
-      <c r="D406" t="inlineStr"/>
+      <c r="D406" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E406" t="inlineStr">
         <is>
           <t>-</t>
@@ -37344,7 +37400,11 @@
           <t>Administration fees – Note 8</t>
         </is>
       </c>
-      <c r="D418" t="inlineStr"/>
+      <c r="D418" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E418" t="inlineStr">
         <is>
           <t>-</t>
@@ -37494,7 +37554,11 @@
           <t>Consulting fees – Note 8</t>
         </is>
       </c>
-      <c r="D420" t="inlineStr"/>
+      <c r="D420" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E420" t="inlineStr">
         <is>
           <t>-</t>
@@ -37642,7 +37706,11 @@
           <t>Rent – Note 8</t>
         </is>
       </c>
-      <c r="D422" t="inlineStr"/>
+      <c r="D422" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E422" t="inlineStr">
         <is>
           <t>-</t>
@@ -38166,7 +38234,11 @@
           <t>Administration fees – Note 7</t>
         </is>
       </c>
-      <c r="D429" t="inlineStr"/>
+      <c r="D429" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E429" t="inlineStr">
         <is>
           <t>-</t>
@@ -38318,7 +38390,11 @@
           <t>Consulting fees – Note 7</t>
         </is>
       </c>
-      <c r="D431" t="inlineStr"/>
+      <c r="D431" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E431" t="inlineStr">
         <is>
           <t>-</t>
@@ -38392,7 +38468,11 @@
           <t>Rent – Note 7</t>
         </is>
       </c>
-      <c r="D432" t="inlineStr"/>
+      <c r="D432" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E432" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/DTWO.xlsx
+++ b/output/pdf_financials_xlsx/DTWO.xlsx
@@ -5443,13 +5443,13 @@
         <v>0</v>
       </c>
       <c r="D114" s="3" t="n">
-        <v>0</v>
+        <v>-0.007269</v>
       </c>
       <c r="E114" s="3" t="n">
-        <v>0</v>
+        <v>0.007269</v>
       </c>
       <c r="F114" s="3" t="n">
-        <v>0</v>
+        <v>-0.5</v>
       </c>
       <c r="G114" s="3" t="n">
         <v>0</v>
@@ -5491,19 +5491,19 @@
         <v>0</v>
       </c>
       <c r="E115" s="3" t="n">
-        <v>0</v>
+        <v>0.007269</v>
       </c>
       <c r="F115" s="3" t="n">
-        <v>0</v>
+        <v>0.190114</v>
       </c>
       <c r="G115" s="3" t="n">
-        <v>0</v>
+        <v>0.049019</v>
       </c>
       <c r="H115" s="3" t="n">
-        <v>0</v>
+        <v>0.100931</v>
       </c>
       <c r="I115" s="3" t="n">
-        <v>0</v>
+        <v>0.013804</v>
       </c>
       <c r="J115" s="3" t="n">
         <v>0</v>
@@ -18282,7 +18282,11 @@
           <t>Proceeds from sale of marketable securities</t>
         </is>
       </c>
-      <c r="D160" t="inlineStr"/>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E160" t="inlineStr">
         <is>
           <t>-</t>
@@ -21684,7 +21688,11 @@
           <t>Proceeds from sale of marketable securities</t>
         </is>
       </c>
-      <c r="D206" t="inlineStr"/>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E206" t="inlineStr">
         <is>
           <t>-</t>
@@ -21830,7 +21838,11 @@
           <t>Purchase of marketable securities</t>
         </is>
       </c>
-      <c r="D208" t="inlineStr"/>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>PurchaseOfInvestment</t>
+        </is>
+      </c>
       <c r="E208" t="inlineStr">
         <is>
           <t>-</t>
@@ -27744,7 +27756,11 @@
           <t>Disposition (purchase) of marketable securities</t>
         </is>
       </c>
-      <c r="D288" t="inlineStr"/>
+      <c r="D288" t="inlineStr">
+        <is>
+          <t>PurchaseOfInvestment</t>
+        </is>
+      </c>
       <c r="E288" t="inlineStr">
         <is>
           <t>-</t>
@@ -29012,7 +29028,11 @@
           <t>Advances on private placement</t>
         </is>
       </c>
-      <c r="D305" t="inlineStr"/>
+      <c r="D305" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E305" t="inlineStr">
         <is>
           <t>-</t>
